--- a/astro-site/public/dl/pack-appcc/07-control-plagas-ddd.xlsx
+++ b/astro-site/public/dl/pack-appcc/07-control-plagas-ddd.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Control Plagas DDD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Plagas DDD" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt formatCode="DD/MM/YYYY" numFmtId="164"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -117,33 +117,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -503,15 +503,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -519,6 +520,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -526,9 +528,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr"/>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -557,9 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -567,9 +565,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -598,13 +594,19 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -612,7 +614,16 @@
   <mergeCells count="1">
     <mergeCell ref="B2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -621,19 +632,19 @@
   <sheetPr>
     <tabColor rgb="00795548"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="14"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="25"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="20"/>
-    <col customWidth="1" max="6" min="6" width="25"/>
-    <col customWidth="1" max="7" min="7" width="18"/>
-    <col customWidth="1" max="8" min="8" width="20"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,6 +661,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -892,6 +904,7 @@
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="9" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
@@ -911,11 +924,19 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Desinsectación,Desratización,Desinfección,Revisión cebos,Inspección visual,Otro"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
-  <pageSetup orientation="landscape"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/pack-appcc/07-control-plagas-ddd.xlsx
+++ b/astro-site/public/dl/pack-appcc/07-control-plagas-ddd.xlsx
@@ -9,8 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Plagas DDD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plano de cebos" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Control Plagas DDD'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Control Plagas DDD'!$A$1:$J$91</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Plano de cebos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Plano de cebos'!$A$1:$H$51</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +79,42 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -92,8 +133,18 @@
         <bgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,11 +166,25 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,10 +204,89 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -505,16 +649,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="2" ht="26" customHeight="1">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Registro de Control de Plagas (DDD)</t>
         </is>
@@ -522,7 +666,7 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla</t>
         </is>
@@ -530,36 +674,36 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>▸ Registra TODAS las actuaciones de control de plagas</t>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>▸ Registra TODAS las actuaciones: desinsectación, desratización, desinfección, revisiones de cebos e inspecciones visuales propias. La hoja trae 80 filas, que es lo que da un año real.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Incluye: desinsectación, desratización y desinfección</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>▸ Anota en la cabecera el Nº ROESB de la empresa contratada. Es su inscripción en el Registro Oficial de Establecimientos y Servicios Biocidas y es lo primero que se comprueba: sin él, la empresa no está habilitada para aplicar biocidas profesionales.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Guarda los certificados de la empresa de control de plagas</t>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>▸ De cada aplicación anota el nº de registro del biocida y su plazo de seguridad en horas. Hasta que ese plazo pase no se puede manipular alimento en la zona tratada.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>▸ Actualiza el plano de ubicación de cebos/trampas</t>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>▸ La pestaña «Plano de cebos» es el croquis numerado de las estaciones: dónde está cada una, de qué tipo es, cuándo se revisó y qué se encontró. Imprímela y dibuja encima la planta del local con los números.</t>
         </is>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Frecuencia recomendada</t>
         </is>
@@ -567,54 +711,74 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>▸ Desinsectación: trimestral (o según necesidad)</t>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>▸ Desratización: revisión mensual de los cebaderos.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>▸ Desratización: mensual revisión de cebos</t>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>▸ Desinsectación: trimestral, o antes si hay indicios.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>▸ Desinfección general: semestral</t>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>▸ Desinfección general: semestral.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>▸ Revisión visual: semanal (buscar indicios)</t>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>▸ Inspección visual propia: semanal, buscando excrementos, roeduras, insectos vivos y puntos de entrada.</t>
         </is>
       </c>
     </row>
     <row r="17"/>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Qué guardar</t>
         </is>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>▸ Contrato en vigor con el Nº ROESB, certificado de cada actuación, fichas de datos de seguridad de los biocidas y el plano de cebos actualizado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>▸ Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/pack-appcc · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
@@ -634,301 +798,2106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Registro de Control de Plagas (DDD)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>Año: ______    Empresa contratada: ________________________________    Nº Contrato: ____________</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Año: ______    Empresa contratada: ________________________    Nº ROESB: ______________    Nº de contrato: ____________</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>El Nº ROESB es la inscripción de la empresa en el Registro Oficial de Establecimientos y Servicios Biocidas. Sin él, el servicio no está habilitado para aplicar biocidas de uso profesional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Tipo Actuación</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Tipo de actuación</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>Empresa / Técnico</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Productos Utilizados</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Zonas Tratadas</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Resultado / Hallazgos</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>Próxima Revisión</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>Nº Certificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="9" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="9" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="9" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="9" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="9" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="9" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="9" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="9" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="9" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="9" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="9" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="9" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="9" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="9" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="9" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>Adjuntar certificados de cada actuación. El plano de cebos debe estar actualizado y accesible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Producto utilizado</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Nº registro del biocida</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Plazo de seguridad (h)</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Zonas tratadas</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Resultado / hallazgos</t>
+        </is>
+      </c>
+      <c r="I4" s="17" t="inlineStr">
+        <is>
+          <t>Próxima revisión</t>
+        </is>
+      </c>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t>Nº certificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>Desratización</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Control de Plagas del Norte S.L. — téc. J.M.</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>Bromadiolona 0,005 % en bloque parafinado</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
+        <is>
+          <t>ES/BIO-00-00000</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>Perímetro exterior, cuarto de residuos y almacén</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>Sin consumo en las 5 estaciones; sin indicios (ejemplo)</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>15/02/2026</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>CERT-2026-0115</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Desinsectación</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Control de Plagas del Norte S.L. — téc. J.M.</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Cipermetrina 10 % microencapsulada</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
+        <is>
+          <t>ES/BIO-00-00000</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Desagües de cocina, cuarto de residuos y falsos techos</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>Tratamiento preventivo trimestral; sin hallazgos (ejemplo)</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>CERT-2026-0116</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>22/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Inspección visual</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Personal propio — jefe de cocina</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Almacén de secos y rodapiés de cocina</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Un saco de harina roído: retirado, lote desechado y avisada la empresa · incidencia INC-004 (ejemplo)</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>29/01/2026</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="18" t="n"/>
+      <c r="B8" s="19" t="n"/>
+      <c r="C8" s="20" t="n"/>
+      <c r="D8" s="20" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="19" t="n"/>
+      <c r="C9" s="20" t="n"/>
+      <c r="D9" s="20" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="21" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="19" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="19" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="18" t="n"/>
+      <c r="J10" s="19" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="19" t="n"/>
+      <c r="C11" s="20" t="n"/>
+      <c r="D11" s="20" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="19" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="19" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="21" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="19" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="19" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="20" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="19" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="20" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="21" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="20" t="n"/>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="20" t="n"/>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="19" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="19" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="21" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="19" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="19" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="20" t="n"/>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="19" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="19" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="20" t="n"/>
+      <c r="H20" s="20" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="19" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="19" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="19" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="20" t="n"/>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="19" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="n"/>
+      <c r="D23" s="20" t="n"/>
+      <c r="E23" s="19" t="n"/>
+      <c r="F23" s="21" t="n"/>
+      <c r="G23" s="20" t="n"/>
+      <c r="H23" s="20" t="n"/>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="19" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="19" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="19" t="n"/>
+      <c r="F24" s="21" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="20" t="n"/>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="19" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="19" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="19" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="20" t="n"/>
+      <c r="H25" s="20" t="n"/>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="19" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="19" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="19" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="19" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="19" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="19" t="n"/>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="19" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="19" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="19" t="n"/>
+      <c r="F28" s="21" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="20" t="n"/>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="19" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="18" t="n"/>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="21" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="20" t="n"/>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="19" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="18" t="n"/>
+      <c r="B32" s="19" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="19" t="n"/>
+      <c r="F32" s="21" t="n"/>
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="20" t="n"/>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="19" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="19" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="19" t="n"/>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="19" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="18" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="19" t="n"/>
+      <c r="F34" s="21" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="19" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="18" t="n"/>
+      <c r="B35" s="19" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="19" t="n"/>
+      <c r="F35" s="21" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="19" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="21" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="19" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="20" t="n"/>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="19" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="19" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="19" t="n"/>
+      <c r="F38" s="21" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="19" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="19" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="19" t="n"/>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="19" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="18" t="n"/>
+      <c r="B41" s="19" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="19" t="n"/>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="19" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="18" t="n"/>
+      <c r="B42" s="19" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="19" t="n"/>
+      <c r="F42" s="21" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="19" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="19" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="19" t="n"/>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="18" t="n"/>
+      <c r="J43" s="19" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="18" t="n"/>
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="19" t="n"/>
+      <c r="F44" s="21" t="n"/>
+      <c r="G44" s="20" t="n"/>
+      <c r="H44" s="20" t="n"/>
+      <c r="I44" s="18" t="n"/>
+      <c r="J44" s="19" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="20" t="n"/>
+      <c r="H45" s="20" t="n"/>
+      <c r="I45" s="18" t="n"/>
+      <c r="J45" s="19" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="18" t="n"/>
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="21" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="18" t="n"/>
+      <c r="J46" s="19" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="18" t="n"/>
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="20" t="n"/>
+      <c r="H47" s="20" t="n"/>
+      <c r="I47" s="18" t="n"/>
+      <c r="J47" s="19" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="18" t="n"/>
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="20" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="21" t="n"/>
+      <c r="G48" s="20" t="n"/>
+      <c r="H48" s="20" t="n"/>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="19" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="18" t="n"/>
+      <c r="B49" s="19" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="19" t="n"/>
+      <c r="F49" s="21" t="n"/>
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="20" t="n"/>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="19" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="18" t="n"/>
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="20" t="n"/>
+      <c r="D50" s="20" t="n"/>
+      <c r="E50" s="19" t="n"/>
+      <c r="F50" s="21" t="n"/>
+      <c r="G50" s="20" t="n"/>
+      <c r="H50" s="20" t="n"/>
+      <c r="I50" s="18" t="n"/>
+      <c r="J50" s="19" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="18" t="n"/>
+      <c r="B51" s="19" t="n"/>
+      <c r="C51" s="20" t="n"/>
+      <c r="D51" s="20" t="n"/>
+      <c r="E51" s="19" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="20" t="n"/>
+      <c r="H51" s="20" t="n"/>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="19" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="18" t="n"/>
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="20" t="n"/>
+      <c r="D52" s="20" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="21" t="n"/>
+      <c r="G52" s="20" t="n"/>
+      <c r="H52" s="20" t="n"/>
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="19" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="18" t="n"/>
+      <c r="B53" s="19" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="21" t="n"/>
+      <c r="G53" s="20" t="n"/>
+      <c r="H53" s="20" t="n"/>
+      <c r="I53" s="18" t="n"/>
+      <c r="J53" s="19" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="18" t="n"/>
+      <c r="B54" s="19" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="21" t="n"/>
+      <c r="G54" s="20" t="n"/>
+      <c r="H54" s="20" t="n"/>
+      <c r="I54" s="18" t="n"/>
+      <c r="J54" s="19" t="n"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="18" t="n"/>
+      <c r="B55" s="19" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="21" t="n"/>
+      <c r="G55" s="20" t="n"/>
+      <c r="H55" s="20" t="n"/>
+      <c r="I55" s="18" t="n"/>
+      <c r="J55" s="19" t="n"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="18" t="n"/>
+      <c r="B56" s="19" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="21" t="n"/>
+      <c r="G56" s="20" t="n"/>
+      <c r="H56" s="20" t="n"/>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="19" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="18" t="n"/>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="20" t="n"/>
+      <c r="D57" s="20" t="n"/>
+      <c r="E57" s="19" t="n"/>
+      <c r="F57" s="21" t="n"/>
+      <c r="G57" s="20" t="n"/>
+      <c r="H57" s="20" t="n"/>
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="19" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="18" t="n"/>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="20" t="n"/>
+      <c r="D58" s="20" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="21" t="n"/>
+      <c r="G58" s="20" t="n"/>
+      <c r="H58" s="20" t="n"/>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="19" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="18" t="n"/>
+      <c r="B59" s="19" t="n"/>
+      <c r="C59" s="20" t="n"/>
+      <c r="D59" s="20" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="21" t="n"/>
+      <c r="G59" s="20" t="n"/>
+      <c r="H59" s="20" t="n"/>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="18" t="n"/>
+      <c r="B60" s="19" t="n"/>
+      <c r="C60" s="20" t="n"/>
+      <c r="D60" s="20" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="21" t="n"/>
+      <c r="G60" s="20" t="n"/>
+      <c r="H60" s="20" t="n"/>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="19" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="18" t="n"/>
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="21" t="n"/>
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20" t="n"/>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="18" t="n"/>
+      <c r="B62" s="19" t="n"/>
+      <c r="C62" s="20" t="n"/>
+      <c r="D62" s="20" t="n"/>
+      <c r="E62" s="19" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="20" t="n"/>
+      <c r="H62" s="20" t="n"/>
+      <c r="I62" s="18" t="n"/>
+      <c r="J62" s="19" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="18" t="n"/>
+      <c r="B63" s="19" t="n"/>
+      <c r="C63" s="20" t="n"/>
+      <c r="D63" s="20" t="n"/>
+      <c r="E63" s="19" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="20" t="n"/>
+      <c r="H63" s="20" t="n"/>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="19" t="n"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="18" t="n"/>
+      <c r="B64" s="19" t="n"/>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="20" t="n"/>
+      <c r="E64" s="19" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="20" t="n"/>
+      <c r="H64" s="20" t="n"/>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="19" t="n"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="18" t="n"/>
+      <c r="B65" s="19" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="19" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="20" t="n"/>
+      <c r="H65" s="20" t="n"/>
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="19" t="n"/>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="18" t="n"/>
+      <c r="B66" s="19" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="19" t="n"/>
+      <c r="F66" s="21" t="n"/>
+      <c r="G66" s="20" t="n"/>
+      <c r="H66" s="20" t="n"/>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="19" t="n"/>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="18" t="n"/>
+      <c r="B67" s="19" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="19" t="n"/>
+      <c r="F67" s="21" t="n"/>
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20" t="n"/>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="19" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="18" t="n"/>
+      <c r="B68" s="19" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="19" t="n"/>
+      <c r="F68" s="21" t="n"/>
+      <c r="G68" s="20" t="n"/>
+      <c r="H68" s="20" t="n"/>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="19" t="n"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="18" t="n"/>
+      <c r="B69" s="19" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20" t="n"/>
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="19" t="n"/>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="18" t="n"/>
+      <c r="B70" s="19" t="n"/>
+      <c r="C70" s="20" t="n"/>
+      <c r="D70" s="20" t="n"/>
+      <c r="E70" s="19" t="n"/>
+      <c r="F70" s="21" t="n"/>
+      <c r="G70" s="20" t="n"/>
+      <c r="H70" s="20" t="n"/>
+      <c r="I70" s="18" t="n"/>
+      <c r="J70" s="19" t="n"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="18" t="n"/>
+      <c r="B71" s="19" t="n"/>
+      <c r="C71" s="20" t="n"/>
+      <c r="D71" s="20" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="21" t="n"/>
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="19" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="18" t="n"/>
+      <c r="B72" s="19" t="n"/>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="20" t="n"/>
+      <c r="H72" s="20" t="n"/>
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="19" t="n"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="18" t="n"/>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="20" t="n"/>
+      <c r="E73" s="19" t="n"/>
+      <c r="F73" s="21" t="n"/>
+      <c r="G73" s="20" t="n"/>
+      <c r="H73" s="20" t="n"/>
+      <c r="I73" s="18" t="n"/>
+      <c r="J73" s="19" t="n"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="18" t="n"/>
+      <c r="B74" s="19" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="21" t="n"/>
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20" t="n"/>
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="19" t="n"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="18" t="n"/>
+      <c r="B75" s="19" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="21" t="n"/>
+      <c r="G75" s="20" t="n"/>
+      <c r="H75" s="20" t="n"/>
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="19" t="n"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="18" t="n"/>
+      <c r="B76" s="19" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="19" t="n"/>
+      <c r="F76" s="21" t="n"/>
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20" t="n"/>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="19" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="18" t="n"/>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="20" t="n"/>
+      <c r="D77" s="20" t="n"/>
+      <c r="E77" s="19" t="n"/>
+      <c r="F77" s="21" t="n"/>
+      <c r="G77" s="20" t="n"/>
+      <c r="H77" s="20" t="n"/>
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="19" t="n"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="18" t="n"/>
+      <c r="B78" s="19" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="19" t="n"/>
+      <c r="F78" s="21" t="n"/>
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="19" t="n"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="18" t="n"/>
+      <c r="B79" s="19" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="19" t="n"/>
+      <c r="F79" s="21" t="n"/>
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20" t="n"/>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="19" t="n"/>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="18" t="n"/>
+      <c r="B80" s="19" t="n"/>
+      <c r="C80" s="20" t="n"/>
+      <c r="D80" s="20" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="21" t="n"/>
+      <c r="G80" s="20" t="n"/>
+      <c r="H80" s="20" t="n"/>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="19" t="n"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="18" t="n"/>
+      <c r="B81" s="19" t="n"/>
+      <c r="C81" s="20" t="n"/>
+      <c r="D81" s="20" t="n"/>
+      <c r="E81" s="19" t="n"/>
+      <c r="F81" s="21" t="n"/>
+      <c r="G81" s="20" t="n"/>
+      <c r="H81" s="20" t="n"/>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="19" t="n"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="18" t="n"/>
+      <c r="B82" s="19" t="n"/>
+      <c r="C82" s="20" t="n"/>
+      <c r="D82" s="20" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="21" t="n"/>
+      <c r="G82" s="20" t="n"/>
+      <c r="H82" s="20" t="n"/>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="19" t="n"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="18" t="n"/>
+      <c r="B83" s="19" t="n"/>
+      <c r="C83" s="20" t="n"/>
+      <c r="D83" s="20" t="n"/>
+      <c r="E83" s="19" t="n"/>
+      <c r="F83" s="21" t="n"/>
+      <c r="G83" s="20" t="n"/>
+      <c r="H83" s="20" t="n"/>
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="19" t="n"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="18" t="n"/>
+      <c r="B84" s="19" t="n"/>
+      <c r="C84" s="20" t="n"/>
+      <c r="D84" s="20" t="n"/>
+      <c r="E84" s="19" t="n"/>
+      <c r="F84" s="21" t="n"/>
+      <c r="G84" s="20" t="n"/>
+      <c r="H84" s="20" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="19" t="n"/>
+    </row>
+    <row r="85"/>
+    <row r="86" ht="12.2" customHeight="1">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>Adjunta el certificado de cada actuación y el plano de cebos actualizado (pestaña «Plano de cebos»). El inspector pide los tres: contrato con el Nº ROESB, certificados y plano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="12.2" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>El «Plazo de seguridad» es el tiempo que debe pasar entre la aplicación del biocida y la vuelta a manipular alimentos en esa zona. Lo fija la ficha del producto y se anota en horas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="12.2" customHeight="1">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>Si aparecen indicios (excrementos, roeduras, insectos vivos), no esperes a la revisión programada: avisa a la empresa el mismo día y abre la incidencia en el registro 11 (Acciones Correctivas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="12.2" customHeight="1">
+      <c r="A89" s="22" t="inlineStr">
+        <is>
+          <t>Las tres primeras filas son EJEMPLOS y lo dicen en «Resultado / observaciones»: bórralas antes de imprimir la hoja. Los nombres de empresa, los nº de certificado y los nº de registro de biocida son inventados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="12.2" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="12.2" customHeight="1">
+      <c r="A91" s="22" t="inlineStr">
         <is>
           <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="7">
+    <mergeCell ref="A86:J86"/>
+    <mergeCell ref="A90:J90"/>
+    <mergeCell ref="A88:J88"/>
+    <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A87:J87"/>
+    <mergeCell ref="A89:J89"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Desinsectación,Desratización,Desinfección,Revisión cebos,Inspección visual,Otro"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="B5:B84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de actuación" error="Elige una actuación de la lista." type="list" errorStyle="stop">
+      <formula1>"Desinsectación,Desratización,Desinfección,Revisión de cebos,Inspección visual,Otro"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Plazo de seguridad" error="Introduce el plazo de seguridad de reentrada en horas, entre 0 y 168. Lo indica la ficha del biocida; hasta que pase, no se puede manipular alimento en la zona tratada." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>168</formula2>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Plano de Cebos y Dispositivos de Control de Plagas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Numera cada estación en el plano de tu local y usa el mismo número en esta tabla. Imprime la hoja y dibuja la planta al dorso o grapa el croquis de la empresa de control de plagas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Nº estación</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Ubicación</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Tipo de dispositivo</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Fecha de instalación</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Fecha última revisión</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Estado / consumo</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Puerta de servicio, exterior derecha</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Cebadero de roedores</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Puerta de servicio, exterior izquierda</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>Cebadero de roedores</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Cuarto de residuos, junto al contenedor</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>Cebadero de roedores</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Almacén de secos, rodapié norte</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>Cebadero de roedores</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Zona de carga y descarga</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Cebadero de roedores</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Cocina, entrada de personal</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Lámpara insectocutora</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>Zona de emplatado</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>Lámpara insectocutora</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Almacén de secos, estante de harinas</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Trampa de feromonas</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>15/01/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>Sin consumo</t>
+        </is>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>J.M. (empresa DDD)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>(ejemplo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="20" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="20" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="20" t="n"/>
+      <c r="C23" s="19" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="19" t="n"/>
+      <c r="G23" s="19" t="n"/>
+      <c r="H23" s="20" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="19" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="19" t="n"/>
+      <c r="G24" s="19" t="n"/>
+      <c r="H24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="19" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="19" t="n"/>
+      <c r="G25" s="19" t="n"/>
+      <c r="H25" s="20" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="19" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="19" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="19" t="n"/>
+      <c r="G27" s="19" t="n"/>
+      <c r="H27" s="20" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="19" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="19" t="n"/>
+      <c r="G29" s="19" t="n"/>
+      <c r="H29" s="20" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="20" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="19" t="n"/>
+      <c r="G31" s="19" t="n"/>
+      <c r="H31" s="20" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="19" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="19" t="n"/>
+      <c r="G32" s="19" t="n"/>
+      <c r="H32" s="20" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="19" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="19" t="n"/>
+      <c r="G33" s="19" t="n"/>
+      <c r="H33" s="20" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="19" t="n"/>
+      <c r="G34" s="19" t="n"/>
+      <c r="H34" s="20" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="23" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="19" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="20" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="19" t="n"/>
+      <c r="G36" s="19" t="n"/>
+      <c r="H36" s="20" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="23" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="20" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="23" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="19" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="19" t="n"/>
+      <c r="G38" s="19" t="n"/>
+      <c r="H38" s="20" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="23" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="19" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="19" t="n"/>
+      <c r="G39" s="19" t="n"/>
+      <c r="H39" s="20" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="19" t="n"/>
+      <c r="G40" s="19" t="n"/>
+      <c r="H40" s="20" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="23" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="19" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="19" t="n"/>
+      <c r="H41" s="20" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="23" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="19" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="19" t="n"/>
+      <c r="G42" s="19" t="n"/>
+      <c r="H42" s="20" t="n"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="23" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="19" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="19" t="n"/>
+      <c r="G43" s="19" t="n"/>
+      <c r="H43" s="20" t="n"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="19" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="20" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>Estaciones con actividad (consumo o captura) en la última revisión:</t>
+        </is>
+      </c>
+      <c r="F46" s="25">
+        <f>COUNTIF(F5:F44,"Consumo parcial")+COUNTIF(F5:F44,"Consumo total")+COUNTIF(F5:F44,"Captura")</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48" ht="12.2" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Si el contador es mayor que cero hay actividad: avisa a la empresa de control de plagas el mismo día, revisa los puntos de entrada y abre la incidencia en el registro 11 (Acciones Correctivas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="12.2" customHeight="1">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>Una estación «Dañada» o «Ausente» también es un hallazgo: hay que reponerla y dejarlo anotado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="12.2" customHeight="1">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Conservar al menos 2 años (trazabilidad y proveedores: 5); el Reg. (CE) 178/2002 exige trazabilidad pero no fija plazo — consulta la guía de prácticas correctas de higiene de tu comunidad autónoma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="12.2" customHeight="1">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>— Pack de Plantillas APPCC · AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A46:E46"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F5:F44">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>OR(F5="ALERTA",F5="RECHAZAR",F5="CAMBIAR",F5="REVISAR",F5="✗",F5="CADUCADO",F5="EXCESO",F5="Consumo total",F5="Captura",F5="Dañado",F5="Ausente")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1" stopIfTrue="1">
+      <formula>OR(F5="VIGILAR",F5="⚠",F5="INCOMPLETO",F5="CADUCA PRONTO",F5="RENOVAR",F5="FALTA CLORO",F5="FALTA TEST",F5="Consumo parcial")</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2" stopIfTrue="1">
+      <formula>OR(F5="OK",F5="✓",F5="Cumple",F5="VIGENTE",F5="Completo",F5="APTO",F5="Sin consumo")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F46">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
+      <formula>F46&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C5:C44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Tipo de dispositivo" error="Elige un tipo de la lista." type="list" errorStyle="stop">
+      <formula1>"Cebadero de roedores,Trampa de captura,Lámpara insectocutora,Trampa de feromonas,Otro"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F5:F44" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Estado / consumo" error="Elige un estado de la lista. El contador del final compara por igualdad exacta, así que un texto libre no suma." type="list" errorStyle="stop">
+      <formula1>"Sin consumo,Consumo parcial,Consumo total,Captura,Dañado,Ausente"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.55" right="0.55" top="0.55" bottom="0.55" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>

--- a/astro-site/public/dl/pack-appcc/07-control-plagas-ddd.xlsx
+++ b/astro-site/public/dl/pack-appcc/07-control-plagas-ddd.xlsx
@@ -2010,12 +2010,12 @@
     <row r="96"/>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A90:J90"/>
     <mergeCell ref="A86:J86"/>
-    <mergeCell ref="A90:J90"/>
     <mergeCell ref="A88:J88"/>
     <mergeCell ref="A91:J91"/>
+    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A87:J87"/>
-    <mergeCell ref="A89:J89"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <dataValidations count="2">
